--- a/public/exports-from-60-with-coowners/29189595.xlsx
+++ b/public/exports-from-60-with-coowners/29189595.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027738</t>
+          <t xml:space="preserve">200027739</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -13714,7 +13714,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189595.xlsx
+++ b/public/exports-from-60-with-coowners/29189595.xlsx
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027739</t>
+          <t xml:space="preserve">200027738</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189595.xlsx
+++ b/public/exports-from-60-with-coowners/29189595.xlsx
@@ -13714,7 +13714,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13864,7 +13864,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14764,7 +14764,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -17891,30 +17891,30 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 11</t>
+          <t xml:space="preserve">Biotekparken 1</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100046682</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>5120</v>
+        <v>798</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558253</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,30 +17966,30 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 13</t>
+          <t xml:space="preserve">Biotekparken 1</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100046682</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J240">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558254</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,30 +18041,30 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 23</t>
+          <t xml:space="preserve">Elise Sørensens Vej 2</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">1352997</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J241">
-        <v>431</v>
+        <v>1771</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558244</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,30 +18116,30 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 23</t>
+          <t xml:space="preserve">Elledevej 59</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">2459947</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J242">
-        <v>3294</v>
+        <v>2103</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558263</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,30 +18191,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Rynkevangen 14C</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">5342669</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J243">
-        <v>1326</v>
+        <v>980</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558264</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,30 +18266,30 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Torvet 3</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">5341684</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J244">
-        <v>408</v>
+        <v>1510</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558248</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18326,12 +18326,12 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Hyldens Kvarter 1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,30 +18351,30 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100430393, 100430394</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>754</v>
+        <v>532</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311562890</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18401,12 +18401,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 27</t>
+          <t xml:space="preserve">Hyldens Kvarter 3</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,30 +18426,30 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100430393, 100430394</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J246">
-        <v>341</v>
+        <v>742</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311562889</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,40 +18491,40 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotekparken 1</t>
+          <t xml:space="preserve">Hyldens Kvarter 5</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046682</t>
+          <t xml:space="preserve">100430394</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J247">
-        <v>798</v>
+        <v>240</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558253</t>
+          <t xml:space="preserve">311562887</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18551,12 +18551,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -18566,40 +18566,40 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotekparken 1</t>
+          <t xml:space="preserve">Hyldens Kvarter 7</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046682</t>
+          <t xml:space="preserve">100430393, 100430394</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J248">
-        <v>683</v>
+        <v>596</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558254</t>
+          <t xml:space="preserve">311562886</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,40 +18641,40 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elise Sørensens Vej 2</t>
+          <t xml:space="preserve">Hyldens Kvarter 9</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352997</t>
+          <t xml:space="preserve">100430394, 100562924</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J249">
-        <v>1771</v>
+        <v>593</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558244</t>
+          <t xml:space="preserve">311562885</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18701,12 +18701,12 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledevej 59</t>
+          <t xml:space="preserve">Herredsåsen 23</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18726,30 +18726,30 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459947</t>
+          <t xml:space="preserve">276426, 276427</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J250">
-        <v>2103</v>
+        <v>1278</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558263</t>
+          <t xml:space="preserve">311576824</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-02-04</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rynkevangen 14C</t>
+          <t xml:space="preserve">Kåstrupvej 45</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,30 +18801,30 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5342669</t>
+          <t xml:space="preserve">276435, 276436</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>980</v>
+        <v>888</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558264</t>
+          <t xml:space="preserve">311582746</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-03-04</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18851,12 +18851,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 3</t>
+          <t xml:space="preserve">Klostermosen 1</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18876,30 +18876,30 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5341684</t>
+          <t xml:space="preserve">275984, 275985</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J252">
-        <v>1510</v>
+        <v>287</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558248</t>
+          <t xml:space="preserve">311586366</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18926,12 +18926,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -18941,40 +18941,40 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 1</t>
+          <t xml:space="preserve">Klostermosen 2</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430393, 100430394</t>
+          <t xml:space="preserve">275985</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J253">
-        <v>532</v>
+        <v>414</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562890</t>
+          <t xml:space="preserve">311586360</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,17 +19016,17 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 3</t>
+          <t xml:space="preserve">Klostermosen 33</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430393, 100430394</t>
+          <t xml:space="preserve">275984, 275985</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -19035,21 +19035,21 @@
         </is>
       </c>
       <c r="J254">
-        <v>742</v>
+        <v>854</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562889</t>
+          <t xml:space="preserve">311586366</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19076,12 +19076,12 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">MNV Bolig</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -19091,40 +19091,40 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 5</t>
+          <t xml:space="preserve">Klostermosen 57</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430394</t>
+          <t xml:space="preserve">275984, 275985</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J255">
-        <v>240</v>
+        <v>854</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562887</t>
+          <t xml:space="preserve">311586366</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,40 +19166,40 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 7</t>
+          <t xml:space="preserve">Klostermosen 9</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430393, 100430394</t>
+          <t xml:space="preserve">275984, 275985</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J256">
-        <v>596</v>
+        <v>854</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562886</t>
+          <t xml:space="preserve">311586366</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,40 +19241,40 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 9</t>
+          <t xml:space="preserve">Centret 9</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4470</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430394, 100562924</t>
+          <t xml:space="preserve">9921582</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J257">
-        <v>593</v>
+        <v>633</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562885</t>
+          <t xml:space="preserve">311594043</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19301,12 +19301,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -19316,40 +19316,40 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herredsåsen 23</t>
+          <t xml:space="preserve">Odinsvej 20</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">276426, 276427</t>
+          <t xml:space="preserve">2472174</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J258">
-        <v>1278</v>
+        <v>2864</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311576824</t>
+          <t xml:space="preserve">311617056</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-04</t>
+          <t xml:space="preserve">2032-07-26</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19376,12 +19376,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kåstrupvej 45</t>
+          <t xml:space="preserve">Bredgade 26</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">276435, 276436</t>
+          <t xml:space="preserve">5341470</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -19410,21 +19410,21 @@
         </is>
       </c>
       <c r="J259">
-        <v>888</v>
+        <v>1011</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582746</t>
+          <t xml:space="preserve">311620368</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-04</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19451,12 +19451,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 1</t>
+          <t xml:space="preserve">Elledevej 63</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,30 +19476,30 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">275984, 275985</t>
+          <t xml:space="preserve">2459948</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>287</v>
+        <v>94</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586366</t>
+          <t xml:space="preserve">311620365</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 2</t>
+          <t xml:space="preserve">Melbygade 2B</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19551,30 +19551,30 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">275985</t>
+          <t xml:space="preserve">2459072</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J261">
-        <v>414</v>
+        <v>308</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586360</t>
+          <t xml:space="preserve">311620364</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19601,12 +19601,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -19616,40 +19616,40 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 33</t>
+          <t xml:space="preserve">Havnepladsen 1</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4591</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">275984, 275985</t>
+          <t xml:space="preserve">2454631</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J262">
-        <v>854</v>
+        <v>69</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586366</t>
+          <t xml:space="preserve">311620788</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19676,12 +19676,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -19691,40 +19691,40 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 57</t>
+          <t xml:space="preserve">Havnepladsen 1</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4591</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">275984, 275985</t>
+          <t xml:space="preserve">2454631</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J263">
-        <v>854</v>
+        <v>65</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586366</t>
+          <t xml:space="preserve">311620787</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19751,12 +19751,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">MNV Bolig</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -19766,40 +19766,40 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 9</t>
+          <t xml:space="preserve">Havnevej 11D</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4591</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">275984, 275985</t>
+          <t xml:space="preserve">2454631</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J264">
-        <v>854</v>
+        <v>200</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586366</t>
+          <t xml:space="preserve">311620790</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,40 +19841,40 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centret 9</t>
+          <t xml:space="preserve">Radiovej 1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">4470</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">9921582</t>
+          <t xml:space="preserve">9416235</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J265">
-        <v>633</v>
+        <v>252</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594043</t>
+          <t xml:space="preserve">311620792</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-21</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,40 +19916,40 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 20</t>
+          <t xml:space="preserve">Radiovej 5</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472174</t>
+          <t xml:space="preserve">9416235</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J266">
-        <v>2864</v>
+        <v>486</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311617056</t>
+          <t xml:space="preserve">311620791</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-26</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,17 +19991,17 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 26</t>
+          <t xml:space="preserve">Algade 14</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4281</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">5341470</t>
+          <t xml:space="preserve">2474884</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,11 +20010,11 @@
         </is>
       </c>
       <c r="J267">
-        <v>1011</v>
+        <v>357</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620368</t>
+          <t xml:space="preserve">311622694</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20024,7 +20024,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledevej 63</t>
+          <t xml:space="preserve">Langagervej 15</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20076,7 +20076,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459948</t>
+          <t xml:space="preserve">5343581</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -20085,11 +20085,11 @@
         </is>
       </c>
       <c r="J268">
-        <v>94</v>
+        <v>653</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620365</t>
+          <t xml:space="preserve">311622692</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,30 +20141,30 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbygade 2B</t>
+          <t xml:space="preserve">Omfartsvejen 5</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4281</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459072</t>
+          <t xml:space="preserve">7544797</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J269">
-        <v>308</v>
+        <v>403</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620364</t>
+          <t xml:space="preserve">311622697</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,30 +20216,30 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 1</t>
+          <t xml:space="preserve">Røsnæsvej 225</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">4591</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2454631</t>
+          <t xml:space="preserve">7761346</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J270">
-        <v>69</v>
+        <v>350</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620788</t>
+          <t xml:space="preserve">311622695</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -20291,30 +20291,30 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnepladsen 1</t>
+          <t xml:space="preserve">Græsmarken 19B</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">4591</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2454631</t>
+          <t xml:space="preserve">8316898</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J271">
-        <v>65</v>
+        <v>362</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620787</t>
+          <t xml:space="preserve">311629060</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20324,7 +20324,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -20366,30 +20366,30 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 11D</t>
+          <t xml:space="preserve">Stadion Alle 13</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">4591</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2454631</t>
+          <t xml:space="preserve">8116851</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J272">
-        <v>200</v>
+        <v>709</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620790</t>
+          <t xml:space="preserve">311629056</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20399,7 +20399,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -20426,12 +20426,12 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Boligselskabet Munkesøparken</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiovej 1</t>
+          <t xml:space="preserve">Esbern Snaresvej 57</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20451,30 +20451,30 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416235</t>
+          <t xml:space="preserve">276009, 276010</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J273">
-        <v>252</v>
+        <v>2341</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620792</t>
+          <t xml:space="preserve">311631835</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2032-09-28</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20501,12 +20501,12 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">FÆLLESORG BOLIGFORENING</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiovej 5</t>
+          <t xml:space="preserve">Frederik Andersensvej 31</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,30 +20526,30 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416235</t>
+          <t xml:space="preserve">420517, 420518</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J274">
-        <v>486</v>
+        <v>2606</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620791</t>
+          <t xml:space="preserve">311669777</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2033-03-28</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20576,12 +20576,12 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Kalundborg almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -20591,17 +20591,17 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 14</t>
+          <t xml:space="preserve">Røsnæsvej 69C</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2474884</t>
+          <t xml:space="preserve">276422, 276423</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -20610,21 +20610,21 @@
         </is>
       </c>
       <c r="J275">
-        <v>357</v>
+        <v>1980</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622694</t>
+          <t xml:space="preserve">311674759</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20651,12 +20651,12 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Kalundborg almennyttige Boligselskab</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langagervej 15</t>
+          <t xml:space="preserve">Røsnæsvej 69D</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,30 +20676,30 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">5343581</t>
+          <t xml:space="preserve">276422, 276423</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J276">
-        <v>653</v>
+        <v>2054</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622692</t>
+          <t xml:space="preserve">311674738</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2033-04-19</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,40 +20741,40 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omfartsvejen 5</t>
+          <t xml:space="preserve">Røsnæsvej 69B</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">7544797</t>
+          <t xml:space="preserve">276423</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J277">
-        <v>403</v>
+        <v>1452</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622697</t>
+          <t xml:space="preserve">311677823</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2033-05-02</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20801,12 +20801,12 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Vestsjællands Almene Boligselskab</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 225</t>
+          <t xml:space="preserve">Lerchenfeldvej 34</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20826,7 +20826,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">7761346</t>
+          <t xml:space="preserve">275085, 275086, 275087</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -20835,21 +20835,21 @@
         </is>
       </c>
       <c r="J278">
-        <v>350</v>
+        <v>1849</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622695</t>
+          <t xml:space="preserve">311722596</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2033-11-15</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20876,12 +20876,12 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg Kommune</t>
+          <t xml:space="preserve">Vestsjællands Almene Boligselskab</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -20891,17 +20891,17 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græsmarken 19B</t>
+          <t xml:space="preserve">Enggårdsvej 5A</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4490</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316898</t>
+          <t xml:space="preserve">276464, 276465, 276466</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -20910,21 +20910,21 @@
         </is>
       </c>
       <c r="J279">
-        <v>362</v>
+        <v>3536</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629060</t>
+          <t xml:space="preserve">311774253</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2034-07-19</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 13</t>
+          <t xml:space="preserve">Frederik Andersensvej 1</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20976,30 +20976,30 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116851</t>
+          <t xml:space="preserve">5342092</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J280">
-        <v>709</v>
+        <v>395</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629056</t>
+          <t xml:space="preserve">311803915</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2034-12-20</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21026,12 +21026,12 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet Munkesøparken</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -21041,40 +21041,40 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esbern Snaresvej 57</t>
+          <t xml:space="preserve">Rosenvænget 11</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">276009, 276010</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J281">
-        <v>2341</v>
+        <v>5120</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311631835</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-28</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">FÆLLESORG BOLIGFORENING</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -21116,40 +21116,40 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Andersensvej 31</t>
+          <t xml:space="preserve">Rosenvænget 13</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">420517, 420518</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J282">
-        <v>2606</v>
+        <v>682</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311669777</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-28</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21176,12 +21176,12 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg almennyttige Boligselskab</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -21191,40 +21191,40 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 69C</t>
+          <t xml:space="preserve">Rosenvænget 23</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">276422, 276423</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J283">
-        <v>1980</v>
+        <v>431</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674759</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalundborg almennyttige Boligselskab</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -21266,17 +21266,17 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 69D</t>
+          <t xml:space="preserve">Rosenvænget 23</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">276422, 276423</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -21285,21 +21285,21 @@
         </is>
       </c>
       <c r="J284">
-        <v>2054</v>
+        <v>3294</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311674738</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,40 +21341,40 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 69B</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">276423</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J285">
-        <v>1452</v>
+        <v>1326</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677823</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-02</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21401,12 +21401,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestsjællands Almene Boligselskab</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -21416,40 +21416,40 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerchenfeldvej 34</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">275085, 275086, 275087</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J286">
-        <v>1849</v>
+        <v>408</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311722596</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-11-15</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21476,12 +21476,12 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestsjællands Almene Boligselskab</t>
+          <t xml:space="preserve">Kalundborg Kommune</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -21491,40 +21491,40 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enggårdsvej 5A</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">4490</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">276464, 276465, 276466</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J287">
-        <v>3536</v>
+        <v>754</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311774253</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,40 +21566,40 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Andersensvej 1</t>
+          <t xml:space="preserve">Rosenvænget 27</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5342092</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J288">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803915</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-20</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
